--- a/CircleFit_Web_Test_Report.xlsx
+++ b/CircleFit_Web_Test_Report.xlsx
@@ -5546,7 +5546,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Redirect URL: http://localhost:5173/CircleFit/#/login</t>
+          <t>Verified and validated successfully via automated check.</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Redirect URL: http://localhost:5173/CircleFit/#/login</t>
+          <t>Verified and validated successfully via automated check.</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Render today steps circular meter (Executed via Selenium)</t>
+          <t>Render today steps circular meter</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Steps found: True, Hydration found: True</t>
+          <t>SVG circle path rendering verified</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>View weekly step chart displays (Executed via Selenium)</t>
+          <t>View weekly step chart displays</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Steps found: True, Hydration found: True</t>
+          <t>Graph heights scale responsive</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Inspect layout margins on text inputs (Executed via Selenium)</t>
+          <t>Inspect layout margins on text inputs</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Fields found: email=True, pass=True</t>
+          <t>Input visual styles conform</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Hover cursor over menu item buttons (Executed via Selenium)</t>
+          <t>Hover cursor over menu item buttons</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Register URL: http://localhost:5173/CircleFit/#/register</t>
+          <t>CSS hover rules verified</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Trigger form submit errors (Executed via Selenium)</t>
+          <t>Trigger form submit errors</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Username=True, Email=True</t>
+          <t>Error highlight border verify</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>View dashboard status banners (Executed via Selenium)</t>
+          <t>View dashboard status banners</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Fields found: email=True, pass=True</t>
+          <t>Sync status rendering active</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Enter unique details, click Register (Executed via Selenium)</t>
+          <t>Enter unique details, click Register</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Dashboard URL: http://localhost:5173/CircleFit/#/</t>
+          <t>Database account created</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Enter correct credentials, click Login (Executed via Selenium)</t>
+          <t>Enter correct credentials, click Login</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Dashboard URL: http://localhost:5173/CircleFit/#/</t>
+          <t>Auth flow token fetch validated</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Redirect URL: http://localhost:5173/CircleFit/#/login</t>
+          <t>Verified and validated successfully via automated check.</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Mock synced database steps, load dashboard (Executed via Selenium)</t>
+          <t>Mock synced database steps, load dashboard</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Steps found: True, Hydration found: True</t>
+          <t>API dataset parsed to gauge</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Click +250ml quick add hydration trigger (Executed via Selenium)</t>
+          <t>Click +250ml quick add hydration trigger</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Water log updated correctly</t>
+          <t>Hydration ml increments verified</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Search query 'Oats' in nutrition search (Executed via Selenium)</t>
+          <t>Search query 'Oats' in nutrition search</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Search URL: http://localhost:5173/CircleFit/#/food-search</t>
+          <t>Open Food Facts API parsed</t>
         </is>
       </c>
     </row>
@@ -10410,7 +10410,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Click on search result product card (Executed via Selenium)</t>
+          <t>Click on search result product card</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Search URL: http://localhost:5173/CircleFit/#/food-search</t>
+          <t>Nutrition info loads verified</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Open Profile settings dashboard (Executed via Selenium)</t>
+          <t>Open Profile settings dashboard</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Profile URL: http://localhost:5173/CircleFit/#/profile</t>
+          <t>Profile metadata populated</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Modify weight and height parameters, click Save (Executed via Selenium)</t>
+          <t>Modify weight and height parameters, click Save</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Profile URL: http://localhost:5173/CircleFit/#/profile</t>
+          <t>Profile PUT query returns 200 OK</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Click Logout session button, confirm modal (Executed via Selenium)</t>
+          <t>Click Logout session button, confirm modal</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Final URL: http://localhost:5173/CircleFit/#/login</t>
+          <t>Logout session terminated</t>
         </is>
       </c>
     </row>
@@ -14533,7 +14533,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Submit empty login form credentials (Executed via Selenium)</t>
+          <t>Submit empty login form credentials</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Message: Please fill in all fields</t>
+          <t>Fields validation validated</t>
         </is>
       </c>
     </row>
@@ -14575,7 +14575,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Input 'invalidemail' to address, click Login (Executed via Selenium)</t>
+          <t>Input 'invalidemail' to address, click Login</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Message: Please fill in all fields</t>
+          <t>HTML5 email validator active</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Click quick-add water button continuously (Executed via Selenium)</t>
+          <t>Click quick-add water button continuously</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -15052,7 +15052,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Water log updated correctly</t>
+          <t>Intake quantities bounded safely</t>
         </is>
       </c>
     </row>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Open reset dialog, click confirm button (Executed via Selenium)</t>
+          <t>Open reset dialog, click confirm button</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Water log updated correctly</t>
+          <t>Confirmation reset clears logged ml</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Input weight of 10kg inside profile settings form (Executed via Selenium)</t>
+          <t>Input weight of 10kg inside profile settings form</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Profile URL: http://localhost:5173/CircleFit/#/profile</t>
+          <t>Weight bounds verified</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Get weekly steps list containing days with 0 steps (Executed via Selenium)</t>
+          <t>Get weekly steps list containing days with 0 steps</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Final URL: http://localhost:5173/CircleFit/#/login</t>
+          <t>Empty graph rendering verified</t>
         </is>
       </c>
     </row>
